--- a/runs/RELX/2026-10-14/bear/scratch/gs_peer_beta/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/gs_peer_beta/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2397.987971514612</v>
+        <v>2450.977688690052</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.087466</v>
+        <v>0.0814532</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.08188375997456002</v>
+        <v>0.07664168067856002</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>12205.72536987247</v>
+        <v>12354.32510415193</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>56227.8707035663</v>
+        <v>61753.58630014669</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>39458.35082798488</v>
+        <v>44293.68715800087</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>51664.07619785735</v>
+        <v>56648.01226215279</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>44667.07619785735</v>
+        <v>49651.01226215279</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>44427.13197656215</v>
+        <v>49519.66169785099</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>25.47785608185603</v>
+        <v>28.39829531705177</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2547.785608185603</v>
+        <v>2839.829531705177</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.08055373220000001</v>
+        <v>0.0248392392</v>
       </c>
     </row>
   </sheetData>
